--- a/out/MLP-Mamba1_repeat_5_000007.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.037571854792519</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003011362564139999</v>
+        <v>-0.0002452957472699927</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.471656286716626</v>
+        <v>2.827897611773278</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.94867912752706</v>
+        <v>5.660166794462667</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.520590323782517</v>
+        <v>0.424055884192473</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.637571854792519</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.513544093537053</v>
+        <v>3.676585371983977</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6509073506056573</v>
+        <v>0.5302078341021269</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.637571854792519</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.294851098966298</v>
+        <v>4.313012499027483</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.9330724375541906</v>
+        <v>0.7600504157268875</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.510456284900738</v>
+        <v>5.303204716127347</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.9982030334549974</v>
+        <v>0.8131033942047913</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.573859157134678</v>
+        <v>6.169417756802826</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.057893280575821</v>
+        <v>0.8617249715308376</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.691519695455984</v>
+        <v>7.079827309796583</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4774075620051145</v>
+        <v>0.3888811184859731</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.587562289793333</v>
+        <v>6.995147008490556</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2305660318000107</v>
+        <v>0.1878111626553322</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.570912393156371</v>
+        <v>6.981584566681281</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1098578497649742</v>
+        <v>0.08948642751101747</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.559878898866955</v>
+        <v>6.972597050322197</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03255011457548362</v>
+        <v>0.02651456745518518</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.037571854792519</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.515003758731787</v>
+        <v>6.936043210671892</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02153116745877032</v>
+        <v>0.01753839762965353</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.525498256555492</v>
+        <v>6.944591594130808</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01101824918062476</v>
+        <v>0.008973590446594742</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.52598922085344</v>
+        <v>6.944990586714146</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005633314631914838</v>
+        <v>0.004588399333231102</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.526232050799596</v>
+        <v>6.94518746929006</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002115034653029544</v>
+        <v>0.001721454496094392</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.524823526424111</v>
+        <v>6.94403925630647</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001150008368162043</v>
+        <v>0.0009363318200520654</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.525008153004784</v>
+        <v>6.944188746384352</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005513109653908299</v>
+        <v>0.0004479960718182472</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.524960005916485</v>
+        <v>6.944148606697292</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003393842911022641</v>
+        <v>0.0002754272084689864</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.525087392849022</v>
+        <v>6.944251442669252</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.000175139602559954</v>
+        <v>0.0001421997895204196</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.525098133141601</v>
+        <v>6.944259267582559</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.292019550909565e-05</v>
+        <v>6.593561228574761e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.525087691140236</v>
+        <v>6.944249846564512</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.128244062155931e-05</v>
+        <v>4.104926959945762e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.525107297121204</v>
+        <v>6.944264978730758</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.064344810800705e-05</v>
+        <v>1.598100299746031e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.52509726441891</v>
+        <v>6.944255861065246</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>6.323060732339969e-06</v>
+        <v>4.264322417369065e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.637571854792519</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.525089249713696</v>
+        <v>6.944248394488252</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-5.494870763551826e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.525085159901208</v>
+        <v>6.944244139310081</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.525079292458523</v>
+        <v>6.944238417031051</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>2.037571854792519</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.525074223103154</v>
+        <v>6.944233347675682</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.525069858129186</v>
+        <v>6.944228982701714</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.525070949375642</v>
+        <v>6.94423007394817</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.525070259768507</v>
+        <v>6.944229384341035</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.525070290080908</v>
+        <v>6.944229414653436</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.037571854792519</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.525070100628398</v>
+        <v>6.944229225200926</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.525070153675102</v>
+        <v>6.944229278247629</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.525070206721804</v>
+        <v>6.944229331294332</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.525070168831302</v>
+        <v>6.944229293403829</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.525070040003596</v>
+        <v>6.944229164576122</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.525069896019687</v>
+        <v>6.944229020592215</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.52506973687958</v>
+        <v>6.944228861452108</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.525069789926283</v>
+        <v>6.94422891449881</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.52506973687958</v>
+        <v>6.944228861452108</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.52506973687958</v>
+        <v>6.944228861452108</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.525069555005171</v>
+        <v>6.944228679577698</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.52506972172338</v>
+        <v>6.944228846295906</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.525069918753989</v>
+        <v>6.944229043326517</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.525069759613881</v>
+        <v>6.944228884186408</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.525069797504383</v>
+        <v>6.94422892207691</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.525069994534993</v>
+        <v>6.94422911910752</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.525069971800692</v>
+        <v>6.944229096373219</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.525069820238683</v>
+        <v>6.944228944811211</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.525069744457682</v>
+        <v>6.944228869030208</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.525069842972984</v>
+        <v>6.944228967545513</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.525069850551086</v>
+        <v>6.944228975123613</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.525070115784599</v>
+        <v>6.944229240357127</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.525069820238683</v>
+        <v>6.944228944811211</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.525070062737898</v>
+        <v>6.944229187310424</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.525070146097001</v>
+        <v>6.944229270669529</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.525069979378792</v>
+        <v>6.94422910395132</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.525070168831302</v>
+        <v>6.944229293403829</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.525069820238683</v>
+        <v>6.944228944811211</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.525069615629972</v>
+        <v>6.944228740202501</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.525069729301478</v>
+        <v>6.944228853874006</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.525069744457682</v>
+        <v>6.944228869030208</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.525069509536568</v>
+        <v>6.944228634109096</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.525069570161371</v>
+        <v>6.944228694733898</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.525069441333665</v>
+        <v>6.944228565906191</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.525069577739471</v>
+        <v>6.944228702312</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.52506975203578</v>
+        <v>6.944228876608308</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.525069896019687</v>
+        <v>6.944229020592215</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.525069729301478</v>
+        <v>6.944228853874006</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.52506972172338</v>
+        <v>6.944228846295906</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.525069433755563</v>
+        <v>6.944228558328091</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.637571854792519</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.525069448911763</v>
+        <v>6.944228573484292</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.525069676254777</v>
+        <v>6.944228800827304</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.525069661098575</v>
+        <v>6.944228785671103</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.525069767191981</v>
+        <v>6.944228891764508</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.525069494380366</v>
+        <v>6.944228618952895</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.637571854792519</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.525069592895672</v>
+        <v>6.944228717468199</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.525069744457682</v>
+        <v>6.944228869030208</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.525069759613881</v>
+        <v>6.944228884186408</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.52506973687958</v>
+        <v>6.944228861452108</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.525069820238683</v>
+        <v>6.944228944811211</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.525069918753989</v>
+        <v>6.944229043326517</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.52506975203578</v>
+        <v>6.944228876608308</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.52506973687958</v>
+        <v>6.944228861452108</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.525069706567178</v>
+        <v>6.944228831139705</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.525069691410977</v>
+        <v>6.944228815983505</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.525069729301478</v>
+        <v>6.944228853874006</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.525069744457682</v>
+        <v>6.944228869030208</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.52506973687958</v>
+        <v>6.944228861452108</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_5_000007.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.4149555617998992</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.037571854792519</v>
+        <v>0.1109984303716906</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716906</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003011362564139999</v>
+        <v>-0.0001790760372062214</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.471656286716626</v>
+        <v>2.064482230637459</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.94867912752706</v>
+        <v>4.132155778228965</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.520590323782517</v>
+        <v>0.3095783196760832</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.513544093537053</v>
+        <v>2.684059367820641</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6509073506056573</v>
+        <v>0.3870736298660361</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.294851098966298</v>
+        <v>3.148677471072756</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.9330724375541906</v>
+        <v>0.5548682127543386</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.510456284900738</v>
+        <v>3.871558709496926</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.9982030334549974</v>
+        <v>0.5935987314109407</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.573859157134678</v>
+        <v>4.503930026193523</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.057893280575821</v>
+        <v>0.6290957476765593</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.691519695455984</v>
+        <v>5.168567011678478</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4774075620051145</v>
+        <v>0.2838985446536909</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.587562289793333</v>
+        <v>5.106746909977893</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2305660318000107</v>
+        <v>0.1371106642096524</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716906</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.570912393156371</v>
+        <v>5.096845745721983</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1098578497649742</v>
+        <v>0.06532853655602751</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716906</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.559878898866955</v>
+        <v>5.090284496469883</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03255011457548362</v>
+        <v>0.01935675287780874</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.037571854792519</v>
+        <v>0.1109984303716906</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.515003758731787</v>
+        <v>5.063598651338072</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02153116745877032</v>
+        <v>0.01280266964988864</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716906</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.525498256555492</v>
+        <v>5.069838231359397</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01101824918062476</v>
+        <v>0.006550108992352238</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.52598922085344</v>
+        <v>5.070128162552195</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005633314631914838</v>
+        <v>0.003348191579880079</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.526232050799596</v>
+        <v>5.070270537275047</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002115034653029544</v>
+        <v>0.001255213387109672</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.524823526424111</v>
+        <v>5.069430989416519</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001150008368162043</v>
+        <v>0.0006822299790564158</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.525008153004784</v>
+        <v>5.069538776651293</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005513109653908299</v>
+        <v>0.0003256076594322647</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.637571854792519</v>
+        <v>0.1109984303716906</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.524960005916485</v>
+        <v>5.069508122654931</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003393842911022641</v>
+        <v>0.0001996626644264884</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.525087392849022</v>
+        <v>5.069581875181285</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.000175139602559954</v>
+        <v>0.000102054392378487</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.525098133141601</v>
+        <v>5.069586247859565</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.292019550909565e-05</v>
+        <v>4.695284280082923e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.637571854792519</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.525087691140236</v>
+        <v>5.069578001819084</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.128244062155931e-05</v>
+        <v>2.82578058218305e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.525107297121204</v>
+        <v>5.069587822106643</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.064344810800705e-05</v>
+        <v>1.015294660927689e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.52509726441891</v>
+        <v>5.0695797345656</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>6.323060732339969e-06</v>
+        <v>2.205584102398162e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.637571854792519</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.525089249713696</v>
+        <v>5.069572816116827</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.525085159901208</v>
+        <v>5.069568395572976</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.525079292458523</v>
+        <v>5.069562817277853</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>2.037571854792519</v>
+        <v>1.03695242254328</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.525074223103154</v>
+        <v>5.069557770656785</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.525069858129186</v>
+        <v>5.069558088937002</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.525070949375642</v>
+        <v>5.069559180183458</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.525070259768507</v>
+        <v>5.069558490576322</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716906</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.525070290080908</v>
+        <v>5.069558520888724</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.037571854792519</v>
+        <v>0.1109984303716906</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.525070100628398</v>
+        <v>5.069558331436214</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716906</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.525070153675102</v>
+        <v>5.069558384482917</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.525070206721804</v>
+        <v>5.069558437529619</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.525070168831302</v>
+        <v>5.069558399639117</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.525070040003596</v>
+        <v>5.06955827081141</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.525069896019687</v>
+        <v>5.069558126827504</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.52506973687958</v>
+        <v>5.069557967687396</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.525069789926283</v>
+        <v>5.069558020734098</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.52506973687958</v>
+        <v>5.069557967687396</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.52506973687958</v>
+        <v>5.069557967687396</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.525069555005171</v>
+        <v>5.069557785812986</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.52506972172338</v>
+        <v>5.069557952531194</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.525069918753989</v>
+        <v>5.069558149561805</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.525069759613881</v>
+        <v>5.069557990421696</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.637571854792519</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.525069797504383</v>
+        <v>5.069558028312198</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.525069994534993</v>
+        <v>5.069558225342808</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.525069971800692</v>
+        <v>5.069558202608508</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.525069820238683</v>
+        <v>5.069558051046499</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.525069744457682</v>
+        <v>5.069557975265496</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.525069842972984</v>
+        <v>5.069558073780801</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.637571854792519</v>
+        <v>0.1109984303716906</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.525069850551086</v>
+        <v>5.069558081358902</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.525070115784599</v>
+        <v>5.069558346592415</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.525069820238683</v>
+        <v>5.069558051046499</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.525070062737898</v>
+        <v>5.069558293545712</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.525070146097001</v>
+        <v>5.069558376904816</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.637571854792519</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.525069979378792</v>
+        <v>5.069558210186608</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.525070168831302</v>
+        <v>5.069558399639117</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.525069820238683</v>
+        <v>5.069558051046499</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.525069615629972</v>
+        <v>5.069557846437789</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.525069729301478</v>
+        <v>5.069557960109295</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.525069744457682</v>
+        <v>5.069557975265496</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.525069509536568</v>
+        <v>5.069557740344384</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.525069570161371</v>
+        <v>5.069557800969187</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.525069441333665</v>
+        <v>5.069557672141479</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.637571854792519</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.525069577739471</v>
+        <v>5.069557808547287</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.52506975203578</v>
+        <v>5.069557982843595</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.4149555617998992</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.525069896019687</v>
+        <v>5.069558126827504</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.4149555617998992</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.525069729301478</v>
+        <v>5.069557960109295</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.52506972172338</v>
+        <v>5.069557952531194</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.525069433755563</v>
+        <v>5.069557664563379</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.637571854792519</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.525069448911763</v>
+        <v>5.069557679719581</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.525069676254777</v>
+        <v>5.069557907062592</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.637571854792519</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.525069661098575</v>
+        <v>5.069557891906391</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.525069767191981</v>
+        <v>5.069557997999796</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716906</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.525069494380366</v>
+        <v>5.069557725188183</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.637571854792519</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.525069592895672</v>
+        <v>5.069557823703487</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.525069744457682</v>
+        <v>5.069557975265496</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.525069759613881</v>
+        <v>5.069557990421696</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.52506973687958</v>
+        <v>5.069557967687396</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.525069820238683</v>
+        <v>5.069558051046499</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.525069918753989</v>
+        <v>5.069558149561805</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.52506975203578</v>
+        <v>5.069557982843595</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.52506973687958</v>
+        <v>5.069557967687396</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.525069706567178</v>
+        <v>5.069557937374993</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.525069691410977</v>
+        <v>5.069557922218793</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.525069729301478</v>
+        <v>5.069557960109295</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.525069744457682</v>
+        <v>5.069557975265496</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998993</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.52506973687958</v>
+        <v>5.069557967687396</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_5_000007.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.443218320608139</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-1</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4609359204769135</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7899999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4469445645809174</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.4154995977878571</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4670852422714233</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4333315789699554</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4270465970039368</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.3975986540317535</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4542222917079926</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.417279988527298</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4226407408714294</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4192865490913391</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4679113626480103</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.3870756030082703</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.3892753720283508</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4153595566749573</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4630165994167328</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4108773171901703</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4329224228858948</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.5282024741172791</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.036952422543281</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.540779709815979</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.762906414714871</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.5657232403755188</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.036952422543281</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4152363836765289</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.3109984303716906</v>
+        <v>0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4380992949008942</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4149555617998992</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4345269203186035</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.411339282989502</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4017948508262634</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5340699553489685</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.1109984303716906</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4046122133731842</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.1109984303716906</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4309498965740204</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4186961054801941</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3546389639377594</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4467661380767822</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4556783437728882</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.1109984303716907</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.555420994758606</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.036952422543281</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.6898081302642822</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.762906414714871</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5059300661087036</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.762906414714871</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.5644129514694214</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.036952422543281</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001790760372062214</v>
+        <v>-0.0001442297056872631</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.064482230637459</v>
+        <v>1.662755492955732</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4151225090026855</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.036952422543281</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.132155778228965</v>
+        <v>3.328081305828174</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3095783196760832</v>
+        <v>0.2493376033478721</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5018714666366577</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.036952422543281</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.684059367820641</v>
+        <v>2.161769372984634</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.3870736298660361</v>
+        <v>0.3117531333942921</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5090134143829346</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.762906414714871</v>
+        <v>-0.16</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.148677471072756</v>
+        <v>2.535977632975608</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.5548682127543386</v>
+        <v>0.446896638262141</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.631639301776886</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.762906414714871</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>3.871558709496926</v>
+        <v>3.118193712197221</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.5935987314109407</v>
+        <v>0.4780908817504419</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.7074922323226929</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.762906414714871</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>4.503930026193523</v>
+        <v>3.627512157246003</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.6290957476765593</v>
+        <v>0.5066799709751724</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.6485782861709595</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.762906414714871</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>5.168567011678478</v>
+        <v>4.162817394577987</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2838985446536909</v>
+        <v>0.2286545814118022</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.6076692342758179</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.036952422543281</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>5.106746909977893</v>
+        <v>4.113026870119093</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1371106642096524</v>
+        <v>0.110429711811827</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.4392960369586945</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.1109984303716906</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>5.096845745721983</v>
+        <v>4.105052370426346</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.06532853655602751</v>
+        <v>0.05261708287207957</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.2775621712207794</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.1109984303716906</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>5.090284496469883</v>
+        <v>4.099767840511219</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01935675287780874</v>
+        <v>0.01558948000753997</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.5582152009010315</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.1109984303716906</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>5.063598651338072</v>
+        <v>4.078274628887007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01280266964988864</v>
+        <v>0.01031015333330494</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4984408617019653</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.1109984303716906</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>5.069838231359397</v>
+        <v>4.083299178444027</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.006550108992352238</v>
+        <v>0.005274903160156426</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.3623518943786621</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>5.070128162552195</v>
+        <v>4.083531734850594</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003348191579880079</v>
+        <v>0.002695874514805839</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4034211039543152</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>5.070270537275047</v>
+        <v>4.083645439858524</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001255213387109672</v>
+        <v>0.001009982673942385</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4696904122829437</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>5.069430989416519</v>
+        <v>4.082968241838502</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0006822299790564158</v>
+        <v>0.0005485790107405222</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.466027557849884</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>5.069538776651293</v>
+        <v>4.083054094460991</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0003256076594322647</v>
+        <v>0.00026123453343704</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.54605633020401</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.1109984303716906</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>5.069508122654931</v>
+        <v>4.083028429691553</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001996626644264884</v>
+        <v>0.0001603044597290868</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4988763630390167</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.3109984303716906</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>5.069581875181285</v>
+        <v>4.083086884481966</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.000102054392378487</v>
+        <v>8.146700922877794e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.3646741509437561</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.3109984303716906</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>5.069586247859565</v>
+        <v>4.083089417997475</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.695284280082923e-05</v>
+        <v>3.696191149297746e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.7912474870681763</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>5.069578001819084</v>
+        <v>4.083081820678642</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.82578058218305e-05</v>
+        <v>2.186207393301694e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.4405593574047089</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.16</v>
       </c>
       <c r="JC59" t="n">
-        <v>5.069587822106643</v>
+        <v>4.083088564442286</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.015294660927689e-05</v>
+        <v>6.65611277636684e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.3899683058261871</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.3109984303716906</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>5.0695797345656</v>
+        <v>4.083081163178829</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>2.205584102398162e-06</v>
+        <v>1.468457874272584e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.5153359770774841</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.3109984303716906</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>5.069572816116827</v>
+        <v>4.083074656452469</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.3619271218776703</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.3109984303716906</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>5.069568395572976</v>
+        <v>4.083070152549514</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.4136688113212585</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.3109984303716906</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>5.069562817277853</v>
+        <v>4.083064719418045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.6456325650215149</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.03695242254328</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>5.069557770656785</v>
+        <v>4.083059672796978</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.8273798823356628</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.762906414714871</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>5.069558088937002</v>
+        <v>4.083059991077194</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.856214702129364</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.036952422543281</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>5.069559180183458</v>
+        <v>4.083061082323651</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.4366524219512939</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.3109984303716906</v>
+        <v>0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>5.069558490576322</v>
+        <v>4.083060392716515</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.337669163942337</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.1109984303716906</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC68" t="n">
-        <v>5.069558520888724</v>
+        <v>4.083060423028917</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.5203894972801208</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.1109984303716906</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>5.069558331436214</v>
+        <v>4.083060233576407</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4890812933444977</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.1109984303716906</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>5.069558384482917</v>
+        <v>4.08306028662311</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.3974886238574982</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>5.069558437529619</v>
+        <v>4.083060339669813</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3933557271957397</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>5.069558399639117</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.3666676878929138</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>5.06955827081141</v>
+        <v>4.083060172951603</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.3845154643058777</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>5.069558126827504</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4545883536338806</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>5.069557967687396</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4292611181735992</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>5.069558020734098</v>
+        <v>4.08305992287429</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.4184129536151886</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>5.069557967687396</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3316203951835632</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>5.069557967687396</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.6070958375930786</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.036952422543281</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>5.069557785812986</v>
+        <v>4.083059687953178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.5872629284858704</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.036952422543281</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>5.069557952531194</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3293256163597107</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.3109984303716906</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>5.069558149561805</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4440700709819794</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.3109984303716906</v>
+        <v>0.16</v>
       </c>
       <c r="JC82" t="n">
-        <v>5.069557990421696</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.5689978003501892</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.3109984303716906</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>5.069558028312198</v>
+        <v>4.08305993045239</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4698932766914368</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.3109984303716906</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>5.069558225342808</v>
+        <v>4.083060127483001</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.3776263892650604</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>5.069558202608508</v>
+        <v>4.0830601047487</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.4218860268592834</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>5.069558051046499</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.4897572994232178</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>5.069557975265496</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.4495253562927246</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>5.069558073780801</v>
+        <v>4.083059975920994</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.5470554828643799</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.1109984303716906</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>5.069558081358902</v>
+        <v>4.083059983499094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4089865982532501</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.036952422543281</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>5.069558346592415</v>
+        <v>4.083060248732608</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.5546711087226868</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.036952422543281</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>5.069558051046499</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.568866491317749</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.036952422543281</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>5.069558293545712</v>
+        <v>4.083060195685905</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3112846910953522</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.036952422543281</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>5.069558376904816</v>
+        <v>4.083060279045009</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.6746240854263306</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.3109984303716906</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>5.069558210186608</v>
+        <v>4.083060112326801</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.2928413450717926</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.3109984303716906</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>5.069558399639117</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.404545783996582</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>5.069558051046499</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.4175305068492889</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>5.069557846437789</v>
+        <v>4.083059748577981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4336241185665131</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>5.069557960109295</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3020636439323425</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>5.069557975265496</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.452802300453186</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>5.069557740344384</v>
+        <v>4.083059642484576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.2996151149272919</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>5.069557800969187</v>
+        <v>4.083059703109379</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.4663175046443939</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.1109984303716907</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>5.069557672141479</v>
+        <v>4.083059574281672</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.639745831489563</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>5.069557808547287</v>
+        <v>4.08305971068748</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4930689036846161</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>5.069557982843595</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3417901992797852</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4149555617998992</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>5.069558126827504</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4585638642311096</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4149555617998992</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>5.069557960109295</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.24618861079216</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>5.069557952531194</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3735837638378143</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>5.069557664563379</v>
+        <v>4.083059566703572</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.5457496643066406</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.3109984303716906</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>5.069557679719581</v>
+        <v>4.083059581859773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3719903230667114</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.036952422543281</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>5.069557907062592</v>
+        <v>4.083059809202784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.545832097530365</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.3109984303716906</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>5.069557891906391</v>
+        <v>4.083059794046584</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.2168305367231369</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.3109984303716906</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>5.069557997999796</v>
+        <v>4.08305990013999</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3927421867847443</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.3109984303716906</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>5.069557725188183</v>
+        <v>4.083059627328375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.5175865292549133</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.3109984303716907</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>5.069557823703487</v>
+        <v>4.08305972584368</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4256742894649506</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.3109984303716907</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>5.069557975265496</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.433984100818634</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>5.069557990421696</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.4612124562263489</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>5.069557967687396</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4951528310775757</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>5.069558051046499</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3582662642002106</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>5.069558149561805</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.3181076049804688</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>5.069557982843595</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4006365835666656</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>5.069557967687396</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3825746178627014</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>5.069557937374993</v>
+        <v>4.083059839515186</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.4504449367523193</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>5.069557922218793</v>
+        <v>4.083059824358986</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.402876615524292</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6149555617998993</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>5.069557960109295</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4271157085895538</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6149555617998993</v>
+        <v>0.6500000000000004</v>
       </c>
       <c r="JC125" t="n">
-        <v>5.069557975265496</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4221817553043365</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6149555617998993</v>
+        <v>1</v>
       </c>
       <c r="JC126" t="n">
-        <v>5.069557967687396</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_5_000007.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.443218320608139</v>
+        <v>0.4432183802127838</v>
       </c>
       <c r="JB2" t="n">
         <v>-1</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.4609359204769135</v>
+        <v>0.4609359800815582</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.7899999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.417279988527298</v>
+        <v>0.4172800183296204</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.8599999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.4226407408714294</v>
+        <v>0.4226407706737518</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.5799999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.4192865490913391</v>
+        <v>0.4192865788936615</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.7199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.3870756030082703</v>
+        <v>0.387075662612915</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.1199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.3892753720283508</v>
+        <v>0.3892754018306732</v>
       </c>
       <c r="JB16" t="n">
         <v>0.16</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.4153595566749573</v>
+        <v>0.4153595864772797</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.1199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.4630165994167328</v>
+        <v>0.4630166590213776</v>
       </c>
       <c r="JB18" t="n">
         <v>0.02000000000000007</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.5282024741172791</v>
+        <v>0.5282025337219238</v>
       </c>
       <c r="JB21" t="n">
         <v>0.5799999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.4152363836765289</v>
+        <v>0.4152364432811737</v>
       </c>
       <c r="JB24" t="n">
         <v>0.16</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.4380992949008942</v>
+        <v>0.4380993843078613</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.411339282989502</v>
+        <v>0.4113393425941467</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.7199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.4017948508262634</v>
+        <v>0.4017949104309082</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.7199999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.4046122133731842</v>
+        <v>0.4046122431755066</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.7199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.4309498965740204</v>
+        <v>0.4309499561786652</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.7199999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.3546389639377594</v>
+        <v>0.3546389937400818</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.5799999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.4467661380767822</v>
+        <v>0.4467662274837494</v>
       </c>
       <c r="JB34" t="n">
         <v>0.3</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.4556783437728882</v>
+        <v>0.4556783735752106</v>
       </c>
       <c r="JB35" t="n">
         <v>0.5799999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.6898081302642822</v>
+        <v>0.6898082494735718</v>
       </c>
       <c r="JB37" t="n">
         <v>0.9999999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.5059300661087036</v>
+        <v>0.5059301257133484</v>
       </c>
       <c r="JB38" t="n">
         <v>0.7199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.5644129514694214</v>
+        <v>0.5644130110740662</v>
       </c>
       <c r="JB39" t="n">
         <v>0.5799999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.4151225090026855</v>
+        <v>0.4151225984096527</v>
       </c>
       <c r="JB40" t="n">
         <v>0.4399999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.5018714666366577</v>
+        <v>0.5018715262413025</v>
       </c>
       <c r="JB41" t="n">
         <v>0.4399999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.631639301776886</v>
+        <v>0.6316393613815308</v>
       </c>
       <c r="JB43" t="n">
         <v>0.1199999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.6076692342758179</v>
+        <v>0.6076693534851074</v>
       </c>
       <c r="JB46" t="n">
         <v>0.4399999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.4392960369586945</v>
+        <v>0.4392959773540497</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.3</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.2775621712207794</v>
+        <v>0.2775622010231018</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.4399999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.5582152009010315</v>
+        <v>0.5582151412963867</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.7199999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.4984408617019653</v>
+        <v>0.4984407424926758</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.7199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.3623518943786621</v>
+        <v>0.3623518049716949</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.7199999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.4034211039543152</v>
+        <v>0.4034210443496704</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.8599999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.4696904122829437</v>
+        <v>0.4696903824806213</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.7199999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.466027557849884</v>
+        <v>0.4660274684429169</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.4399999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.54605633020401</v>
+        <v>0.5460562705993652</v>
       </c>
       <c r="JB55" t="n">
         <v>0.1600000000000001</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.4988763630390167</v>
+        <v>0.4988762438297272</v>
       </c>
       <c r="JB56" t="n">
         <v>0.4399999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.3646741509437561</v>
+        <v>0.3646740019321442</v>
       </c>
       <c r="JB57" t="n">
         <v>0.4399999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.4405593574047089</v>
+        <v>0.4405592679977417</v>
       </c>
       <c r="JB59" t="n">
         <v>0.16</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.3899683058261871</v>
+        <v>0.3899681866168976</v>
       </c>
       <c r="JB60" t="n">
         <v>0.16</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.5153359770774841</v>
+        <v>0.5153358578681946</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.7199999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.3619271218776703</v>
+        <v>0.3619270622730255</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.4399999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.4136688113212585</v>
+        <v>0.4136687517166138</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.1600000000000001</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.856214702129364</v>
+        <v>0.8562148213386536</v>
       </c>
       <c r="JB66" t="n">
         <v>0.4399999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.4366524219512939</v>
+        <v>0.4366525411605835</v>
       </c>
       <c r="JB67" t="n">
         <v>0.3</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.5203894972801208</v>
+        <v>0.5203893780708313</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.8599999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.4890812933444977</v>
+        <v>0.4890812337398529</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.8599999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.3974886238574982</v>
+        <v>0.3974884748458862</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.8599999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.3933557271957397</v>
+        <v>0.3933555781841278</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.3666676878929138</v>
+        <v>0.3666675388813019</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.3845154643058777</v>
+        <v>0.3845153450965881</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.4545883536338806</v>
+        <v>0.4545882046222687</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.4292611181735992</v>
+        <v>0.4292609989643097</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.4184129536151886</v>
+        <v>0.418412834405899</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.7199999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.3316203951835632</v>
+        <v>0.3316202759742737</v>
       </c>
       <c r="JB78" t="n">
         <v>0.16</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.6070958375930786</v>
+        <v>0.6070957183837891</v>
       </c>
       <c r="JB79" t="n">
         <v>0.1600000000000001</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.5872629284858704</v>
+        <v>0.5872628092765808</v>
       </c>
       <c r="JB80" t="n">
         <v>0.1600000000000001</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.3293256163597107</v>
+        <v>0.3293254673480988</v>
       </c>
       <c r="JB81" t="n">
         <v>0.4399999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.4440700709819794</v>
+        <v>0.444069892168045</v>
       </c>
       <c r="JB82" t="n">
         <v>0.16</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.5689978003501892</v>
+        <v>0.5689976811408997</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.1199999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.4698932766914368</v>
+        <v>0.469893217086792</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.7199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.3776263892650604</v>
+        <v>0.3776262700557709</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.4399999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.4218860268592834</v>
+        <v>0.4218858480453491</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.7199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.4897572994232178</v>
+        <v>0.4897571802139282</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.4399999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.4495253562927246</v>
+        <v>0.4495252072811127</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.4399999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.5470554828643799</v>
+        <v>0.5470553636550903</v>
       </c>
       <c r="JB89" t="n">
         <v>0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.4089865982532501</v>
+        <v>0.4089864790439606</v>
       </c>
       <c r="JB90" t="n">
         <v>0.4399999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.5546711087226868</v>
+        <v>0.5546709299087524</v>
       </c>
       <c r="JB91" t="n">
         <v>0.4399999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.568866491317749</v>
+        <v>0.5688663721084595</v>
       </c>
       <c r="JB92" t="n">
         <v>0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.3112846910953522</v>
+        <v>0.3112845420837402</v>
       </c>
       <c r="JB93" t="n">
         <v>0.4399999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.6746240854263306</v>
+        <v>0.6746240258216858</v>
       </c>
       <c r="JB94" t="n">
         <v>0.1600000000000001</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.2928413450717926</v>
+        <v>0.2928412854671478</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.7199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.404545783996582</v>
+        <v>0.4045456349849701</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.4175305068492889</v>
+        <v>0.417530357837677</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.9999999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.4336241185665131</v>
+        <v>0.4336239397525787</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.3020636439323425</v>
+        <v>0.3020635545253754</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.7199999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.452802300453186</v>
+        <v>0.4528021812438965</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.4399999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.2996151149272919</v>
+        <v>0.2996149957180023</v>
       </c>
       <c r="JB101" t="n">
         <v>0.4399999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.4663175046443939</v>
+        <v>0.4663176238536835</v>
       </c>
       <c r="JB102" t="n">
         <v>0.7199999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.639745831489563</v>
+        <v>0.6397457718849182</v>
       </c>
       <c r="JB103" t="n">
         <v>0.4399999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.4930689036846161</v>
+        <v>0.4930687248706818</v>
       </c>
       <c r="JB104" t="n">
         <v>0.7199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.3417901992797852</v>
+        <v>0.3417900502681732</v>
       </c>
       <c r="JB105" t="n">
         <v>0.4399999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.4585638642311096</v>
+        <v>0.4585636854171753</v>
       </c>
       <c r="JB106" t="n">
         <v>0.1600000000000001</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.24618861079216</v>
+        <v>0.2461885213851929</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.4399999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.3735837638378143</v>
+        <v>0.3735838532447815</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.4399999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.5457496643066406</v>
+        <v>0.545749843120575</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.4399999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.3719903230667114</v>
+        <v>0.3719902038574219</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.4399999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.545832097530365</v>
+        <v>0.5458319783210754</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.4399999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.2168305367231369</v>
+        <v>0.2168304473161697</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.5799999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.3927421867847443</v>
+        <v>0.3927423357963562</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.5799999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.5175865292549133</v>
+        <v>0.517586350440979</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.7199999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.4256742894649506</v>
+        <v>0.4256741106510162</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.4399999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.433984100818634</v>
+        <v>0.4339838624000549</v>
       </c>
       <c r="JB116" t="n">
         <v>0.4399999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.4612124562263489</v>
+        <v>0.4612122774124146</v>
       </c>
       <c r="JB117" t="n">
         <v>0.3</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.4951528310775757</v>
+        <v>0.4951525926589966</v>
       </c>
       <c r="JB118" t="n">
         <v>0.3</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.3582662642002106</v>
+        <v>0.3582660555839539</v>
       </c>
       <c r="JB119" t="n">
         <v>0.16</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.3181076049804688</v>
+        <v>0.3181074261665344</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.7199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.4006365835666656</v>
+        <v>0.4006363749504089</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.8599999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.3825746178627014</v>
+        <v>0.3825744688510895</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.8599999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.4504449367523193</v>
+        <v>0.4504447877407074</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.5799999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.402876615524292</v>
+        <v>0.4028764367103577</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.4271157085895538</v>
+        <v>0.4271155893802643</v>
       </c>
       <c r="JB125" t="n">
         <v>0.6500000000000004</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.4221817553043365</v>
+        <v>0.4221816658973694</v>
       </c>
       <c r="JB126" t="n">
         <v>1</v>
